--- a/reports/2026-07_組合品項銷量與換算.xlsx
+++ b/reports/2026-07_組合品項銷量與換算.xlsx
@@ -10,6 +10,7 @@
   <sheets>
     <sheet name="組合品項銷量" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="換算1入與12入盒數" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="搖搖杯品號與銷量" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="201">
   <si>
     <r>
       <rPr>
@@ -4246,7 +4247,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">依口味彙整　－　組合品項共帶出多少盒（</t>
+      <t xml:space="preserve">依口味彙整　－　單獨販售 </t>
     </r>
     <r>
       <rPr>
@@ -4257,7 +4258,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">vs. </t>
     </r>
     <r>
       <rPr>
@@ -4267,7 +4268,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">入）與多少散裝 </t>
+      <t xml:space="preserve">組合帶出，兩種 </t>
     </r>
     <r>
       <rPr>
@@ -4278,7 +4279,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t xml:space="preserve">SKU </t>
     </r>
     <r>
       <rPr>
@@ -4288,8 +4289,14 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">入</t>
-    </r>
+      <t xml:space="preserve">分開列示</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">單獨販售</t>
+  </si>
+  <si>
+    <t xml:space="preserve">組合帶出</t>
   </si>
   <si>
     <t xml:space="preserve">口味</t>
@@ -4361,34 +4368,44 @@
       <rPr>
         <b val="true"/>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">盒數 </t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(12</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">入 </t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">入</t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">包</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -4401,29 +4418,63 @@
       <rPr>
         <b val="true"/>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">散裝 </t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">入組 </t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">入 </t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">盒</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">總盒數</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">總散裝 </t>
     </r>
     <r>
       <rPr>
@@ -4577,20 +4628,59 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">入盒裝之組合內容物</t>
+      <t xml:space="preserve">入盒裝品項（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">500g </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">袋裝 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">贈品），單獨販售與組合帶出分開列示</t>
     </r>
   </si>
   <si>
     <t xml:space="preserve">項目</t>
   </si>
   <si>
-    <t xml:space="preserve">數量</t>
-  </si>
-  <si>
     <t xml:space="preserve">單位</t>
   </si>
   <si>
-    <t xml:space="preserve">來源組合</t>
+    <t xml:space="preserve">組合來源</t>
   </si>
   <si>
     <r>
@@ -4695,10 +4785,34 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">經典搖搖杯</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P00xxS</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">經典搖搖杯（各色，明細見第 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分頁）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">P0003S–P0017S</t>
   </si>
   <si>
     <t xml:space="preserve">個</t>
@@ -4874,7 +4988,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">盒數 </t>
+      <t xml:space="preserve">總盒數 </t>
     </r>
     <r>
       <rPr>
@@ -4893,7 +5007,144 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">散裝 </t>
+      <t xml:space="preserve">總散裝。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「單獨販售」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= Shopify </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">變體報表銷量 − </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">App </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">組合包拆出的元件；「組合帶出」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">商品型組合內含盒數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ App </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">組合包拆出的元件。兩者相加即該口味 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月全部出貨量。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">驗算：</t>
     </r>
     <r>
       <rPr>
@@ -4912,19 +5163,209 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">入。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2. A </t>
+      <t xml:space="preserve">入 合計 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">436 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">包、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">入組 合計 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">243 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">盒。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">436 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">與 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Shopify </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">變體報表 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">入 總和相同；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">243 = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">變體報表 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">入 總和 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">149 + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">商品型組合內含 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">94 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">盒（商品型組合以組合商品出貨，不進變體報表）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4. A </t>
     </r>
     <r>
       <rPr>
@@ -5009,7 +5450,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">入），數量列於「非盒裝內容物」與 </t>
+      <t xml:space="preserve">入），數量列於 </t>
     </r>
     <r>
       <rPr>
@@ -5040,16 +5481,16 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">3. B </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">區「散裝 </t>
+      <t xml:space="preserve">5. B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">區「組合帶出－</t>
     </r>
     <r>
       <rPr>
@@ -5175,6 +5616,1289 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">6. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「未指定」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">盒來自晚安舒緩（任選</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">盒）中 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">筆未寫入 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Select Your Flavor </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">屬性的訂單（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#2528 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">數量 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#2530 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">數量 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）；其餘 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">組已記錄口味：開心果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">黑芝麻 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">組、香蕉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">開心果 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">組。若要精準分攤，需回頭比對這 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">組的出貨明細。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">香蕉牛奶 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">入組於 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月訂單中同時出現 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VG00B2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">與舊碼 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BA0001 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">兩種 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SKU</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，已合併計算；植感醇黑可可的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">入 變體在期間內由「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">入組」改名為「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">入」，變體報表因而拆成兩列（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20 + 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），本表已合併為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">22 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">盒。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AGUGU</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">｜經典搖搖杯　顏色 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">品號 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 7 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月銷量</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">期間：</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026/07/01 – 2026/07/31</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（台北時間）　｜　品號取自 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Shopify </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">商品變體 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SKU</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（每個顏色為獨立商品，變體為 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Default Title</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">全部顏色品號對照與 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月銷量</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">顏色 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">款式</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SKU</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（品號）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">售價</t>
+  </si>
+  <si>
+    <t xml:space="preserve">經典粉色搖搖杯</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P0004S</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">新手入門組 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×5</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">經典白色搖搖杯</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P0007S</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">新手入門組 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、入門全配組 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">經典白色搖搖杯 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">提環</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">P0017S</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">經典黑色搖搖杯 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">提環</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">P0016S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">經典藍色搖搖杯</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P0003S</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">新手入門組 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×1</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">經典黑色搖搖杯</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P0008S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">經典綠色搖搖杯</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P0006S</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月無銷售</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">經典橘色搖搖杯</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P0009S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">經典紫色搖搖杯</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P0010S</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">經典太空灰搖搖杯 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">提環</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">P0015S</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「單獨販售」為顧客單買搖搖杯的數量；「組合帶出」為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">App </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">組合包（新手入門組、入門全配組）隨組附的搖搖杯，於結帳時拆成獨立品項，因此 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Shopify </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">商品報表的數字是兩者相加。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. 7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月共出貨 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個搖搖杯，其中 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">59%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）是隨組合附贈；粉色 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個為最大宗，其中 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個來自新手入門組。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">綠色（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P0006S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）、橘色（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P0009S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）、紫色（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P0010S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）、太空灰提環（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P0015S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月完全沒有銷售，四色皆未被任何組合選用，建議檢視庫存與是否續留。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">4. </t>
     </r>
     <r>
@@ -5184,273 +6908,45 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">「未指定」</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">盒來自晚安舒緩（任選</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">盒）中 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">筆未寫入 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Select Your Flavor </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">屬性的訂單（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">#2528 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">數量 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">#2530 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">數量 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）；其餘 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">7 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">組已記錄口味：開心果</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">黑芝麻 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">組、香蕉</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">開心果 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">組。若要精準分攤，需回頭比對這 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">組的出貨明細。</t>
+      <t xml:space="preserve">品號缺號說明：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P0005S </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未使用；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P0011S / P0013S / P0014S </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">屬蛋白飲商品，非搖搖杯。</t>
     </r>
   </si>
   <si>
@@ -5471,218 +6967,83 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">本表僅涵蓋「組合品項」帶出的數量，不含單獨購買 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">入 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ 12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">入組的銷量。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">香蕉牛奶 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">入組於 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">7 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月訂單中同時出現 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">VG00B2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">與舊碼 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">BA0001 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">兩種 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SKU</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，已合併計算；植感醇黑可可 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">入 的變體名稱為「</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">入」而非「</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">入組」，建議統一命名以利日後報表比對。</t>
+      <t xml:space="preserve">提環款（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P0015S–P0017S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）售價 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$399</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，一般款（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P0003S–P0010S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）售價 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$299</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。</t>
     </r>
   </si>
 </sst>
@@ -5798,7 +7159,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5814,7 +7175,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E2F3"/>
-        <bgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFDDEBF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -5831,8 +7192,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFDDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor rgb="FFD9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -5885,7 +7258,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="37">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5974,24 +7347,64 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -6024,7 +7437,7 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFF2CC"/>
-      <rgbColor rgb="FFF2F2F2"/>
+      <rgbColor rgb="FFDDEBF7"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -6038,8 +7451,8 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFF2F2F2"/>
+      <rgbColor rgb="FFE2EFDA"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -6940,14 +8353,18 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6960,7 +8377,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>77</v>
       </c>
@@ -7348,431 +8765,1107 @@
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
-    </row>
-    <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="21" t="s">
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="22"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="B25" s="22" t="s">
+      <c r="E25" s="23"/>
+      <c r="F25" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="C25" s="22" t="s">
+      <c r="G25" s="24"/>
+      <c r="H25" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="I25" s="25"/>
+      <c r="J25" s="25"/>
+    </row>
+    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="D25" s="21" t="s">
+      <c r="B26" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="E25" s="21" t="s">
+      <c r="C26" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="F25" s="21" t="s">
+      <c r="D26" s="27" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
+      <c r="E26" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="F26" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="G26" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="H26" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="I26" s="29" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="E26" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="F26" s="8" t="n">
-        <f aca="false">D26*12+E26</f>
-        <v>348</v>
+      <c r="J26" s="29" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D27" s="8" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="E27" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="G27" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="F27" s="8" t="n">
-        <f aca="false">D27*12+E27</f>
-        <v>314</v>
+      <c r="H27" s="30" t="n">
+        <f aca="false">E27+G27</f>
+        <v>60</v>
+      </c>
+      <c r="I27" s="30" t="n">
+        <f aca="false">D27+F27</f>
+        <v>73</v>
+      </c>
+      <c r="J27" s="30" t="n">
+        <f aca="false">H27*12+I27</f>
+        <v>793</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F28" s="8" t="n">
-        <f aca="false">D28*12+E28</f>
-        <v>222</v>
+        <v>26</v>
+      </c>
+      <c r="G28" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="H28" s="30" t="n">
+        <f aca="false">E28+G28</f>
+        <v>29</v>
+      </c>
+      <c r="I28" s="30" t="n">
+        <f aca="false">D28+F28</f>
+        <v>67</v>
+      </c>
+      <c r="J28" s="30" t="n">
+        <f aca="false">H28*12+I28</f>
+        <v>415</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="E29" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="G29" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="H29" s="30" t="n">
+        <f aca="false">E29+G29</f>
         <v>24</v>
       </c>
-      <c r="F29" s="8" t="n">
-        <f aca="false">D29*12+E29</f>
-        <v>192</v>
+      <c r="I29" s="30" t="n">
+        <f aca="false">D29+F29</f>
+        <v>68</v>
+      </c>
+      <c r="J29" s="30" t="n">
+        <f aca="false">H29*12+I29</f>
+        <v>356</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="E30" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="F30" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="F30" s="8" t="n">
-        <f aca="false">D30*12+E30</f>
-        <v>168</v>
+      <c r="G30" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="H30" s="30" t="n">
+        <f aca="false">E30+G30</f>
+        <v>42</v>
+      </c>
+      <c r="I30" s="30" t="n">
+        <f aca="false">D30+F30</f>
+        <v>80</v>
+      </c>
+      <c r="J30" s="30" t="n">
+        <f aca="false">H30*12+I30</f>
+        <v>584</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F31" s="8" t="n">
-        <f aca="false">D31*12+E31</f>
-        <v>141</v>
+        <v>24</v>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H31" s="30" t="n">
+        <f aca="false">E31+G31</f>
+        <v>20</v>
+      </c>
+      <c r="I31" s="30" t="n">
+        <f aca="false">D31+F31</f>
+        <v>46</v>
+      </c>
+      <c r="J31" s="30" t="n">
+        <f aca="false">H31*12+I31</f>
+        <v>286</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D32" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="G32" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="E32" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="F32" s="8" t="n">
-        <f aca="false">D32*12+E32</f>
-        <v>140</v>
+      <c r="H32" s="30" t="n">
+        <f aca="false">E32+G32</f>
+        <v>14</v>
+      </c>
+      <c r="I32" s="30" t="n">
+        <f aca="false">D32+F32</f>
+        <v>43</v>
+      </c>
+      <c r="J32" s="30" t="n">
+        <f aca="false">H32*12+I32</f>
+        <v>211</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D33" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H33" s="30" t="n">
+        <f aca="false">E33+G33</f>
+        <v>26</v>
+      </c>
+      <c r="I33" s="30" t="n">
+        <f aca="false">D33+F33</f>
+        <v>58</v>
+      </c>
+      <c r="J33" s="30" t="n">
+        <f aca="false">H33*12+I33</f>
+        <v>370</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E33" s="8" t="n">
+      <c r="H34" s="30" t="n">
+        <f aca="false">E34+G34</f>
+        <v>22</v>
+      </c>
+      <c r="I34" s="30" t="n">
+        <f aca="false">D34+F34</f>
+        <v>1</v>
+      </c>
+      <c r="J34" s="30" t="n">
+        <f aca="false">H34*12+I34</f>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="B35" s="32" t="s">
+        <v>141</v>
+      </c>
+      <c r="C35" s="32" t="s">
+        <v>141</v>
+      </c>
+      <c r="D35" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="F33" s="8" t="n">
-        <f aca="false">D33*12+E33</f>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="B34" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="C34" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="D34" s="25" t="n">
+      <c r="E35" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="E34" s="25" t="n">
+      <c r="H35" s="30" t="n">
+        <f aca="false">E35+G35</f>
+        <v>6</v>
+      </c>
+      <c r="I35" s="30" t="n">
+        <f aca="false">D35+F35</f>
         <v>0</v>
       </c>
-      <c r="F34" s="25" t="n">
-        <f aca="false">D34*12+E34</f>
+      <c r="J35" s="30" t="n">
+        <f aca="false">H35*12+I35</f>
         <v>72</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="11" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="B35" s="12"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="13" t="n">
-        <f aca="false">SUM(D26:D34)</f>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="13" t="n">
+        <f aca="false">SUM(D27:D35)</f>
+        <v>255</v>
+      </c>
+      <c r="E36" s="13" t="n">
+        <f aca="false">SUM(E27:E35)</f>
+        <v>120</v>
+      </c>
+      <c r="F36" s="13" t="n">
+        <f aca="false">SUM(F27:F35)</f>
+        <v>181</v>
+      </c>
+      <c r="G36" s="13" t="n">
+        <f aca="false">SUM(G27:G35)</f>
         <v>123</v>
       </c>
-      <c r="E35" s="13" t="n">
-        <f aca="false">SUM(E26:E34)</f>
-        <v>181</v>
-      </c>
-      <c r="F35" s="13" t="n">
-        <f aca="false">SUM(F26:F34)</f>
-        <v>1657</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D36" s="26" t="str">
-        <f aca="false">IF(D35=D22,"✓ 與 A 區盒數一致","✗ 不一致")</f>
-        <v>✓ 與 A 區盒數一致</v>
-      </c>
-      <c r="E36" s="26"/>
-      <c r="F36" s="26"/>
-    </row>
-    <row r="38" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="B39" s="5" t="s">
+      <c r="H36" s="13" t="n">
+        <f aca="false">SUM(H27:H35)</f>
+        <v>243</v>
+      </c>
+      <c r="I36" s="13" t="n">
+        <f aca="false">SUM(I27:I35)</f>
+        <v>436</v>
+      </c>
+      <c r="J36" s="13" t="n">
+        <f aca="false">SUM(J27:J35)</f>
+        <v>3352</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D37" s="34" t="str">
+        <f aca="false">IF(AND(G36=D22,F36=181),"✓ 組合帶出盒數與 A 區一致；1入 總計 436 包、12入組 總計 243 盒，與 Shopify 變體報表相符","✗ 不一致")</f>
+        <v>✓ 組合帶出盒數與 A 區一致；1入 總計 436 包、12入組 總計 243 盒，與 Shopify 變體報表相符</v>
+      </c>
+      <c r="E37" s="34"/>
+      <c r="F37" s="34"/>
+      <c r="G37" s="34"/>
+      <c r="H37" s="34"/>
+      <c r="I37" s="34"/>
+      <c r="J37" s="34"/>
+    </row>
+    <row r="39" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B40" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C39" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="F39" s="4"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="B40" s="7" t="s">
+      <c r="C40" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="C40" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D40" s="10" t="s">
+      <c r="D40" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E40" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="F40" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="G40" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="E40" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="F40" s="6"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="B41" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="B41" s="7" t="s">
+      <c r="C41" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="C41" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D41" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="E41" s="6" t="s">
+      <c r="D41" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F41" s="30" t="n">
+        <f aca="false">D41+E41</f>
+        <v>9</v>
+      </c>
+      <c r="G41" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="F41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="6"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="15" t="s">
         <v>150</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="C42" s="8" t="n">
+      <c r="C42" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F42" s="30" t="n">
+        <f aca="false">D42+E42</f>
         <v>10</v>
       </c>
-      <c r="D42" s="10" t="s">
+      <c r="G42" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="E42" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="6"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B43" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="B43" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C43" s="8" t="n">
+      <c r="C43" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F43" s="30" t="n">
+        <f aca="false">D43+E43</f>
+        <v>17</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="6"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="D43" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="F43" s="6"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="19" t="s">
+      <c r="F44" s="30" t="n">
+        <f aca="false">D44+E44</f>
+        <v>2</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="6"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="B45" s="19"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="19"/>
-      <c r="E45" s="19"/>
-      <c r="F45" s="19"/>
-    </row>
-    <row r="46" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="B46" s="20"/>
-      <c r="C46" s="20"/>
-      <c r="D46" s="20"/>
-      <c r="E46" s="20"/>
-      <c r="F46" s="20"/>
+      <c r="B46" s="19"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="19"/>
+      <c r="F46" s="19"/>
+      <c r="G46" s="19"/>
+      <c r="H46" s="19"/>
+      <c r="I46" s="19"/>
+      <c r="J46" s="19"/>
     </row>
     <row r="47" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="20" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B47" s="20"/>
       <c r="C47" s="20"/>
       <c r="D47" s="20"/>
       <c r="E47" s="20"/>
       <c r="F47" s="20"/>
+      <c r="G47" s="20"/>
+      <c r="H47" s="20"/>
+      <c r="I47" s="20"/>
+      <c r="J47" s="20"/>
     </row>
     <row r="48" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="20" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B48" s="20"/>
       <c r="C48" s="20"/>
       <c r="D48" s="20"/>
       <c r="E48" s="20"/>
       <c r="F48" s="20"/>
+      <c r="G48" s="20"/>
+      <c r="H48" s="20"/>
+      <c r="I48" s="20"/>
+      <c r="J48" s="20"/>
     </row>
     <row r="49" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="20" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B49" s="20"/>
       <c r="C49" s="20"/>
       <c r="D49" s="20"/>
       <c r="E49" s="20"/>
       <c r="F49" s="20"/>
+      <c r="G49" s="20"/>
+      <c r="H49" s="20"/>
+      <c r="I49" s="20"/>
+      <c r="J49" s="20"/>
     </row>
     <row r="50" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="20" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B50" s="20"/>
       <c r="C50" s="20"/>
       <c r="D50" s="20"/>
       <c r="E50" s="20"/>
       <c r="F50" s="20"/>
+      <c r="G50" s="20"/>
+      <c r="H50" s="20"/>
+      <c r="I50" s="20"/>
+      <c r="J50" s="20"/>
     </row>
     <row r="51" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="20" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B51" s="20"/>
       <c r="C51" s="20"/>
       <c r="D51" s="20"/>
       <c r="E51" s="20"/>
       <c r="F51" s="20"/>
+      <c r="G51" s="20"/>
+      <c r="H51" s="20"/>
+      <c r="I51" s="20"/>
+      <c r="J51" s="20"/>
+    </row>
+    <row r="52" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="B52" s="20"/>
+      <c r="C52" s="20"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="20"/>
+      <c r="G52" s="20"/>
+      <c r="H52" s="20"/>
+      <c r="I52" s="20"/>
+      <c r="J52" s="20"/>
+    </row>
+    <row r="53" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="B53" s="20"/>
+      <c r="C53" s="20"/>
+      <c r="D53" s="20"/>
+      <c r="E53" s="20"/>
+      <c r="F53" s="20"/>
+      <c r="G53" s="20"/>
+      <c r="H53" s="20"/>
+      <c r="I53" s="20"/>
+      <c r="J53" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="20">
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="A45:F45"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A48:F48"/>
-    <mergeCell ref="A49:F49"/>
-    <mergeCell ref="A50:F50"/>
-    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="D37:J37"/>
+    <mergeCell ref="A39:J39"/>
+    <mergeCell ref="G40:J40"/>
+    <mergeCell ref="G41:J41"/>
+    <mergeCell ref="G42:J42"/>
+    <mergeCell ref="G43:J43"/>
+    <mergeCell ref="G44:J44"/>
+    <mergeCell ref="A46:J46"/>
+    <mergeCell ref="A47:J47"/>
+    <mergeCell ref="A48:J48"/>
+    <mergeCell ref="A49:J49"/>
+    <mergeCell ref="A50:J50"/>
+    <mergeCell ref="A51:J51"/>
+    <mergeCell ref="A52:J52"/>
+    <mergeCell ref="A53:J53"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="35" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>299</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="30" t="n">
+        <f aca="false">D6+E6</f>
+        <v>7</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>299</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="30" t="n">
+        <f aca="false">D7+E7</f>
+        <v>3</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>399</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="30" t="n">
+        <f aca="false">D8+E8</f>
+        <v>3</v>
+      </c>
+      <c r="G8" s="6"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>399</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="30" t="n">
+        <f aca="false">D9+E9</f>
+        <v>2</v>
+      </c>
+      <c r="G9" s="6"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>299</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="30" t="n">
+        <f aca="false">D10+E10</f>
+        <v>1</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>299</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="30" t="n">
+        <f aca="false">D11+E11</f>
+        <v>1</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="31" t="s">
+        <v>187</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>188</v>
+      </c>
+      <c r="C12" s="33" t="n">
+        <v>299</v>
+      </c>
+      <c r="D12" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="30" t="n">
+        <f aca="false">D12+E12</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="36" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="31" t="s">
+        <v>190</v>
+      </c>
+      <c r="B13" s="32" t="s">
+        <v>191</v>
+      </c>
+      <c r="C13" s="33" t="n">
+        <v>299</v>
+      </c>
+      <c r="D13" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="30" t="n">
+        <f aca="false">D13+E13</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="36" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="31" t="s">
+        <v>192</v>
+      </c>
+      <c r="B14" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="C14" s="33" t="n">
+        <v>299</v>
+      </c>
+      <c r="D14" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="30" t="n">
+        <f aca="false">D14+E14</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="36" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="B15" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="C15" s="33" t="n">
+        <v>399</v>
+      </c>
+      <c r="D15" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="30" t="n">
+        <f aca="false">D15+E15</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="36" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="13" t="n">
+        <f aca="false">SUM(D6:D15)</f>
+        <v>7</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <f aca="false">SUM(E6:E15)</f>
+        <v>10</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <f aca="false">SUM(F6:F15)</f>
+        <v>17</v>
+      </c>
+      <c r="G16" s="12"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+    </row>
+    <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+    </row>
+    <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+    </row>
+    <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+    </row>
+    <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+    </row>
+    <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
